--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536125_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536125_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>V. MUNOZ QUINONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,58 +890,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.215</v>
+        <v>1.263</v>
       </c>
       <c r="E6" t="n">
-        <v>1.215</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.9994</v>
       </c>
       <c r="G6" t="n">
-        <v>1.215</v>
+        <v>1.0118</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.7608</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215</v>
+        <v>0.251</v>
       </c>
       <c r="J6" t="n">
-        <v>1.215</v>
+        <v>0.9517</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.6567</v>
       </c>
       <c r="L6" t="n">
-        <v>1.215</v>
+        <v>-0.705</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.0602</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8959</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.956</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9749</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1448</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.7237</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.5181</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2056</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. MUNOZ QUINONES</t>
+          <t>F. TORREBLANCA CATALAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.048</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9514</v>
+        <v>-1.0409</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9994</v>
+        <v>0.3438</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2032</v>
+        <v>-0.5357</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7608</v>
+        <v>-0.717</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.964</v>
+        <v>0.1813</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2634</v>
+        <v>-0.532</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6567</v>
+        <v>-0.4345</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.92</v>
+        <v>-0.0975</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0602</v>
+        <v>-0.0037</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8959</v>
+        <v>-0.2825</v>
       </c>
       <c r="O9" t="n">
-        <v>0.956</v>
+        <v>0.2788</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9749</v>
+        <v>1.7549</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1699</v>
+        <v>-0.195</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1448</v>
+        <v>1.9499</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7237</v>
+        <v>-0.6962</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5181</v>
+        <v>-0.314</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2056</v>
+        <v>-0.3822</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. TORREBLANCA CATALAN</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-1.893</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0409</v>
+        <v>-0.5931</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3438</v>
+        <v>-1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5357</v>
+        <v>-0.6827</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.717</v>
+        <v>-1.2677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1813</v>
+        <v>0.5849</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.532</v>
+        <v>-0.9515</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4345</v>
+        <v>-0.992</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0975</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0037</v>
+        <v>0.2688</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2825</v>
+        <v>-0.2756</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2788</v>
+        <v>0.5444</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7549</v>
+        <v>0.195</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.195</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9499</v>
+        <v>0.195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6962</v>
+        <v>0.1462</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.314</v>
+        <v>0.0799</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3822</v>
+        <v>0.0664</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2201</v>
+        <v>-1.5515</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2201</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>H. FIGUEROA ALVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.893</v>
+        <v>-3.837</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5931</v>
+        <v>-4.7985</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3</v>
+        <v>0.9616</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6827</v>
+        <v>0.4659</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2677</v>
+        <v>0.1942</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5849</v>
+        <v>0.2718</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9515</v>
+        <v>-0.895</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.992</v>
+        <v>-0.619</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>-0.276</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2688</v>
+        <v>1.3609</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2756</v>
+        <v>0.8132</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5444</v>
+        <v>0.5477</v>
       </c>
       <c r="P11" t="n">
-        <v>0.195</v>
+        <v>-2.7298</v>
       </c>
       <c r="Q11" t="n">
+        <v>-3.8997</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.1699</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.2201</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1462</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.0799</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.0664</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-1.5515</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.2786</v>
-      </c>
       <c r="X11" t="n">
-        <v>-1.8301</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ALVAREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,157 +1388,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.837</v>
+        <v>11.4225</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7985</v>
+        <v>1.1397</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9616</v>
+        <v>10.2829</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4659</v>
+        <v>18.586</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1942</v>
+        <v>5.771500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2718</v>
+        <v>12.8145</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.895</v>
+        <v>14.5395</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.619</v>
+        <v>6.538100000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.276</v>
+        <v>8.001300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3609</v>
+        <v>4.0467</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8132</v>
+        <v>-0.7665000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5477</v>
+        <v>4.813</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.7298</v>
+        <v>-2.9247</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8997</v>
+        <v>-20.4735</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1699</v>
+        <v>17.5487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.353</v>
+        <v>-0.3668000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0039</v>
+        <v>-0.2606000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3492</v>
+        <v>-0.1058999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2201</v>
+        <v>-3.8719</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>7.3344</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>play_by_play_2536125_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-11.2064</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
+          <t>CLÍNICA PONFERRADA SDP</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4225</v>
+        <v>4.1187</v>
       </c>
       <c r="E13" t="n">
-        <v>1.139700000000001</v>
+        <v>2.0453</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2829</v>
+        <v>2.0734</v>
       </c>
       <c r="G13" t="n">
-        <v>18.586</v>
+        <v>0.1628</v>
       </c>
       <c r="H13" t="n">
-        <v>5.771500000000001</v>
+        <v>0.2551</v>
       </c>
       <c r="I13" t="n">
-        <v>12.8145</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>14.5394</v>
+        <v>0.5631</v>
       </c>
       <c r="K13" t="n">
-        <v>6.538100000000001</v>
+        <v>0.6686</v>
       </c>
       <c r="L13" t="n">
-        <v>8.001300000000001</v>
+        <v>-0.1055</v>
       </c>
       <c r="M13" t="n">
-        <v>4.046700000000001</v>
+        <v>-0.4003</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7665000000000003</v>
+        <v>-0.4135</v>
       </c>
       <c r="O13" t="n">
-        <v>4.813</v>
+        <v>0.0132</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9247</v>
+        <v>1.3649</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.4735</v>
+        <v>-0.9749</v>
       </c>
       <c r="R13" t="n">
-        <v>17.5487</v>
+        <v>2.3398</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3668000000000001</v>
+        <v>0.1508</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2606000000000002</v>
+        <v>-0.2616</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1058999999999998</v>
+        <v>0.4124</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.8719</v>
+        <v>2.4401</v>
       </c>
       <c r="W13" t="n">
-        <v>7.3344</v>
+        <v>2.7187</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.2064</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>-0.2786</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2536125_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1187</v>
+        <v>4.025</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0453</v>
+        <v>4.2499</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0734</v>
+        <v>-0.2249</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1628</v>
+        <v>1.697</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2551</v>
+        <v>4.1789</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-2.4819</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5631</v>
+        <v>4.5424</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6686</v>
+        <v>5.1419</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1055</v>
+        <v>-0.5995</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4003</v>
+        <v>-2.8454</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4135</v>
+        <v>-0.963</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0132</v>
+        <v>-1.8824</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3649</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3398</v>
+        <v>1.9499</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1508</v>
+        <v>0.445</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2616</v>
+        <v>0.4373</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4124</v>
+        <v>0.0077</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4401</v>
+        <v>1.883</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7187</v>
+        <v>1.2201</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2786</v>
+        <v>0.6629</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.025</v>
+        <v>0.8657</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2499</v>
+        <v>0.2542</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2249</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.697</v>
+        <v>-1.8003</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1789</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4819</v>
+        <v>-0.9056</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5424</v>
+        <v>-1.259</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1419</v>
+        <v>-0.619</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5995</v>
+        <v>-0.64</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8454</v>
+        <v>-0.5413</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.963</v>
+        <v>-0.2756</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8824</v>
+        <v>-0.2656</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>1.5599</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9499</v>
+        <v>1.5599</v>
       </c>
       <c r="S15" t="n">
-        <v>0.445</v>
+        <v>0.1646</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4373</v>
+        <v>0.2932</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0077</v>
+        <v>-0.1286</v>
       </c>
       <c r="V15" t="n">
-        <v>1.883</v>
+        <v>0.9415</v>
       </c>
       <c r="W15" t="n">
         <v>1.2201</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6629</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>S. SOAREZ PEREYRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,64 +1716,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8657</v>
+        <v>-0.1971</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2542</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.5938</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8003</v>
+        <v>-0.3297</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.7381</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9056</v>
+        <v>0.4083</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.259</v>
+        <v>-0.5985</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.619</v>
+        <v>-0.5985</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5413</v>
+        <v>0.2688</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2756</v>
+        <v>-0.1395</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2656</v>
+        <v>0.4083</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5599</v>
+        <v>0.39</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5599</v>
+        <v>0.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1646</v>
+        <v>0.0212</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2932</v>
+        <v>-0.1923</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1286</v>
+        <v>0.2136</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9415</v>
+        <v>-0.2786</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2786</v>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. SOAREZ PEREYRA</t>
+          <t>J. IJEH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1971</v>
+        <v>-0.9576</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0.2116</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5938</v>
+        <v>-1.1692</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3297</v>
+        <v>-0.6222</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7381</v>
+        <v>-0.0877</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4083</v>
+        <v>-0.5345</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5985</v>
+        <v>0.3241</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5985</v>
+        <v>0.3241</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2688</v>
+        <v>-0.9463</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1395</v>
+        <v>-0.4118</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4083</v>
+        <v>-0.5345</v>
       </c>
       <c r="P17" t="n">
-        <v>0.39</v>
+        <v>1.1699</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.39</v>
+        <v>1.1699</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0212</v>
+        <v>-0.2852</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1923</v>
+        <v>-0.1125</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2136</v>
+        <v>-0.1728</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. IJEH</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9576</v>
+        <v>-1.3011</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2116</v>
+        <v>-0.1993</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1692</v>
+        <v>-1.1018</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6222</v>
+        <v>-0.9513</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0877</v>
+        <v>-0.4135</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5345</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3241</v>
+        <v>0.1395</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3241</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6805</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9463</v>
+        <v>-1.0908</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4118</v>
+        <v>-1.2335</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5345</v>
+        <v>0.1427</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1699</v>
+        <v>1.5599</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1699</v>
+        <v>1.5599</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2852</v>
+        <v>-0.1325</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1125</v>
+        <v>-0.3388</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1728</v>
+        <v>0.2063</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2201</v>
+        <v>-1.7772</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2201</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>M. YIMBU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3011</v>
+        <v>-1.7703</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1993</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1018</v>
+        <v>-2.541</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9513</v>
+        <v>-2.0797</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4135</v>
+        <v>-1.1953</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.8844</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1395</v>
+        <v>0.0161</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8201000000000001</v>
+        <v>-0.7129</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6805</v>
+        <v>0.729</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0908</v>
+        <v>-2.0959</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2335</v>
+        <v>-0.4824</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1427</v>
+        <v>-1.6135</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5599</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9248</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5599</v>
+        <v>2.1448</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1325</v>
+        <v>1.4209</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3388</v>
+        <v>0.9607</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2063</v>
+        <v>0.4602</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7772</v>
+        <v>-0.3315</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.7187</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7772</v>
+        <v>-3.0501</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. YIMBU</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7703</v>
+        <v>-2.4172</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7707000000000001</v>
+        <v>-1.2381</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.541</v>
+        <v>-1.1791</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0797</v>
+        <v>-4.1445</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1953</v>
+        <v>-1.3838</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8844</v>
+        <v>-2.7607</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0161</v>
+        <v>-1.7778</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7129</v>
+        <v>-0.3518</v>
       </c>
       <c r="L20" t="n">
-        <v>0.729</v>
+        <v>-1.426</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0959</v>
+        <v>-2.3666</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4824</v>
+        <v>-1.032</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6135</v>
+        <v>-1.3347</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7799</v>
+        <v>2.5348</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9248</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1448</v>
+        <v>2.5348</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4209</v>
+        <v>-0.529</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9607</v>
+        <v>-0.6803</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4602</v>
+        <v>0.1513</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3315</v>
+        <v>-0.2786</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7187</v>
+        <v>1.2201</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0501</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4172</v>
+        <v>-2.7749</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2381</v>
+        <v>-4.3777</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1791</v>
+        <v>1.6028</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1445</v>
+        <v>-3.4543</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3838</v>
+        <v>-2.7756</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7607</v>
+        <v>-0.6786</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7778</v>
+        <v>-1.8405</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3518</v>
+        <v>-2.4965</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.426</v>
+        <v>0.656</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3666</v>
+        <v>-1.6138</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.032</v>
+        <v>-0.2791</v>
       </c>
       <c r="O21" t="n">
         <v>-1.3347</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5348</v>
+        <v>-0.195</v>
       </c>
       <c r="Q21" t="n">
+        <v>-2.9248</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.7298</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.1762</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.6629</v>
+      </c>
+      <c r="W21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.5348</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.529</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.6803</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.1513</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.2201</v>
-      </c>
       <c r="X21" t="n">
-        <v>-1.4986</v>
+        <v>0.6629</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7749</v>
+        <v>-3.9622</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3777</v>
+        <v>-5.0496</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6028</v>
+        <v>1.0874</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4543</v>
+        <v>-1.7281</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7756</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6786</v>
+        <v>-0.8585</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8405</v>
+        <v>0.1612</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.4965</v>
+        <v>-0.4543</v>
       </c>
       <c r="L22" t="n">
-        <v>0.656</v>
+        <v>0.6155</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6138</v>
+        <v>-1.8893</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2791</v>
+        <v>-0.4152</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3347</v>
+        <v>-1.4741</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.195</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9248</v>
+        <v>-4.8746</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7298</v>
+        <v>2.5348</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2114</v>
+        <v>0.1057</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3875</v>
+        <v>-0.3362</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1762</v>
+        <v>0.4419</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6629</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6629</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9622</v>
+        <v>-6.1683</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0496</v>
+        <v>-6.159</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0874</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7281</v>
+        <v>-5.3357</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-1.8474</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8585</v>
+        <v>-3.4883</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1612</v>
+        <v>-4.317</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4543</v>
+        <v>-0.955</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6155</v>
+        <v>-3.3621</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8893</v>
+        <v>-1.0186</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4152</v>
+        <v>-0.8924</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4741</v>
+        <v>-0.1262</v>
       </c>
       <c r="P23" t="n">
         <v>-2.3398</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.8746</v>
+        <v>-3.8997</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5348</v>
+        <v>1.5599</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1057</v>
+        <v>-0.3229</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3362</v>
+        <v>-0.0509</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4419</v>
+        <v>-0.272</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.8301</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.1086</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,152 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1683</v>
+        <v>-10.5393</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.159</v>
+        <v>-10.2828</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.2564999999999994</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.3357</v>
+        <v>-18.586</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8474</v>
+        <v>-5.7716</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4883</v>
+        <v>-12.8143</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.317</v>
+        <v>-4.0464</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.955</v>
+        <v>0.7666999999999994</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3621</v>
+        <v>-4.8131</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0186</v>
+        <v>-14.5395</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8924</v>
+        <v>-6.538</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1262</v>
+        <v>-8.0015</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3398</v>
+        <v>2.9249</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8997</v>
+        <v>-17.5487</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5599</v>
+        <v>20.4735</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3229</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0509</v>
+        <v>0.1061000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.272</v>
+        <v>1.1438</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8301</v>
+        <v>3.871600000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1086</v>
+        <v>11.2063</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536125_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-10.5393</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-10.2828</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.2564999999999994</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-18.586</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-5.7716</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-12.8143</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-4.0464</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.7666999999999994</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-4.8131</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-14.5395</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-6.538</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-8.0015</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.9249</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-17.5487</v>
-      </c>
-      <c r="R25" t="n">
-        <v>20.4735</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.1061000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.1438</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.871600000000001</v>
-      </c>
-      <c r="W25" t="n">
-        <v>11.2063</v>
-      </c>
-      <c r="X25" t="n">
         <v>-7.334600000000001</v>
       </c>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
